--- a/web/accessibility/data/fhr-distances.xlsx
+++ b/web/accessibility/data/fhr-distances.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FHR assigned distances" sheetId="1" r:id="R3f4d6e5059644988"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FHR assigned distances" sheetId="1" r:id="R9be26eeb20d84933"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,26 +16,21 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="0.0"/>
   </x:numFmts>
-  <x:fonts count="4">
+  <x:fonts count="3">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
     </x:font>
     <x:font>
       <x:sz val="11"/>
-      <x:color rgb="FF23313B"/>
-      <x:name val="Helvetica Neue"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
     </x:font>
     <x:font>
       <x:b/>
       <x:sz val="11"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Helvetica Neue"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color rgb="FF687780"/>
-      <x:name val="Helvetica Neue"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
     </x:font>
   </x:fonts>
   <x:fills count="3">
@@ -47,11 +42,11 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF253B4B"/>
+        <x:fgColor rgb="FFFFFFFF"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="4">
+  <x:borders count="2">
     <x:border>
       <x:left/>
       <x:right/>
@@ -61,79 +56,50 @@
     </x:border>
     <x:border>
       <x:left/>
-      <x:right style="thin">
-        <x:color rgb="FFFFFFFF"/>
-      </x:right>
-      <x:top/>
-      <x:bottom/>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFFFFFFF"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="FFFFFFFF"/>
-      </x:right>
-      <x:top/>
-      <x:bottom/>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFFFFFFF"/>
-      </x:left>
       <x:right/>
       <x:top/>
-      <x:bottom/>
+      <x:bottom style="thin">
+        <x:color rgb="FFBFBFBF"/>
+      </x:bottom>
       <x:diagonal/>
     </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="17">
+  <x:cellXfs count="14">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+      <x:alignment horizontal="left" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="0"/>
     </x:xf>
   </x:cellXfs>
@@ -154,7 +120,7 @@
     <x:tableColumn id="5" name="Straight-line km"/>
     <x:tableColumn id="6" name="Road network km"/>
   </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <x:tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
@@ -353,1528 +319,1528 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="17.780000686645508" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="34.439998626708984" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="34.439998626708984" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="34.439998626708984" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="16.110000610351562" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="16.110000610351562" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="15.5600004196167" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="60" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15.5600004196167" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="43.33000183105469" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="17.780000686645508" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="17.780000686645508" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="138.88999938964844" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="62" customHeight="1">
+    <x:row r="1" ht="33" customHeight="1">
       <x:c r="A1" s="11" t="str">
         <x:v>CBO province</x:v>
       </x:c>
-      <x:c r="B1" s="12" t="str">
+      <x:c r="B1" s="11" t="str">
         <x:v>CBO</x:v>
       </x:c>
-      <x:c r="C1" s="12" t="str">
+      <x:c r="C1" s="11" t="str">
         <x:v>FHR school province</x:v>
       </x:c>
-      <x:c r="D1" s="12" t="str">
+      <x:c r="D1" s="11" t="str">
         <x:v>FHR school</x:v>
       </x:c>
-      <x:c r="E1" s="12" t="str">
+      <x:c r="E1" s="11" t="str">
         <x:v>Straight-line km</x:v>
       </x:c>
-      <x:c r="F1" s="13" t="str">
+      <x:c r="F1" s="11" t="str">
         <x:v>Road network km</x:v>
       </x:c>
-      <x:c r="H1" s="16" t="str">
+      <x:c r="H1" s="13" t="str">
         <x:v>Distances are in kilometres.</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="42" customHeight="1">
-      <x:c r="A2" s="5" t="str">
+    <x:row r="2" ht="15" customHeight="1">
+      <x:c r="A2" s="6" t="str">
         <x:v>Eastern Cape</x:v>
       </x:c>
-      <x:c r="B2" s="5" t="str">
+      <x:c r="B2" s="6" t="str">
         <x:v>Doxa Family Care NPC</x:v>
       </x:c>
-      <x:c r="C2" s="5" t="str">
+      <x:c r="C2" s="6" t="str">
         <x:v>Eastern Cape</x:v>
       </x:c>
-      <x:c r="D2" s="5" t="str">
+      <x:c r="D2" s="6" t="str">
         <x:v>Emfundweni Primary School</x:v>
       </x:c>
-      <x:c r="E2" s="7" t="n">
+      <x:c r="E2" s="8" t="n">
         <x:v>1.159</x:v>
       </x:c>
-      <x:c r="F2" s="7" t="n">
+      <x:c r="F2" s="8" t="n">
         <x:v>1.387</x:v>
       </x:c>
-      <x:c r="H2" s="16" t="str">
+      <x:c r="H2" s="13" t="str">
         <x:v>Connections follow the recorded FHR–CBO assignments.</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="42" customHeight="1">
-      <x:c r="A3" s="5" t="str">
+    <x:row r="3" ht="15" customHeight="1">
+      <x:c r="A3" s="6" t="str">
         <x:v>Eastern Cape</x:v>
       </x:c>
-      <x:c r="B3" s="5" t="str">
+      <x:c r="B3" s="6" t="str">
         <x:v>Doxa Family Care NPC</x:v>
       </x:c>
-      <x:c r="C3" s="5" t="str">
+      <x:c r="C3" s="6" t="str">
         <x:v>Eastern Cape</x:v>
       </x:c>
-      <x:c r="D3" s="5" t="str">
+      <x:c r="D3" s="6" t="str">
         <x:v>Garrett Primary School</x:v>
       </x:c>
-      <x:c r="E3" s="7" t="n">
+      <x:c r="E3" s="8" t="n">
         <x:v>0.203</x:v>
       </x:c>
-      <x:c r="F3" s="7" t="n">
+      <x:c r="F3" s="8" t="n">
         <x:v>0.245</x:v>
       </x:c>
-      <x:c r="H3" s="16" t="str">
+      <x:c r="H3" s="13" t="str">
         <x:v>Source: https://graeme-dor.github.io/fhr-cbo-mapping-project/accessibility/</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="42" customHeight="1">
-      <x:c r="A4" s="5" t="str">
+    <x:row r="4" ht="15" customHeight="1">
+      <x:c r="A4" s="6" t="str">
         <x:v>Eastern Cape</x:v>
       </x:c>
-      <x:c r="B4" s="5" t="str">
+      <x:c r="B4" s="6" t="str">
         <x:v>Doxa Family Care NPC</x:v>
       </x:c>
-      <x:c r="C4" s="5" t="str">
+      <x:c r="C4" s="6" t="str">
         <x:v>Eastern Cape</x:v>
       </x:c>
-      <x:c r="D4" s="5" t="str">
+      <x:c r="D4" s="6" t="str">
         <x:v>Ndzondelelo High School</x:v>
       </x:c>
-      <x:c r="E4" s="7" t="n">
+      <x:c r="E4" s="8" t="n">
         <x:v>0.635</x:v>
       </x:c>
-      <x:c r="F4" s="7" t="n">
+      <x:c r="F4" s="8" t="n">
         <x:v>0.819</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="42" customHeight="1">
-      <x:c r="A5" s="5" t="str">
+    <x:row r="5" ht="15" customHeight="1">
+      <x:c r="A5" s="6" t="str">
         <x:v>Free State</x:v>
       </x:c>
-      <x:c r="B5" s="5" t="str">
+      <x:c r="B5" s="6" t="str">
         <x:v>My Dignity Restored Shelter for the Abused Women and Children</x:v>
       </x:c>
-      <x:c r="C5" s="5" t="str">
+      <x:c r="C5" s="6" t="str">
         <x:v>Free State</x:v>
       </x:c>
-      <x:c r="D5" s="5" t="str">
+      <x:c r="D5" s="6" t="str">
         <x:v>Mmulakgoro Intermediate School</x:v>
       </x:c>
-      <x:c r="E5" s="7" t="n">
+      <x:c r="E5" s="8" t="n">
         <x:v>0.321</x:v>
       </x:c>
-      <x:c r="F5" s="7" t="n">
+      <x:c r="F5" s="8" t="n">
         <x:v>0.314</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="42" customHeight="1">
-      <x:c r="A6" s="5" t="str">
+    <x:row r="6" ht="15" customHeight="1">
+      <x:c r="A6" s="6" t="str">
         <x:v>Free State</x:v>
       </x:c>
-      <x:c r="B6" s="5" t="str">
+      <x:c r="B6" s="6" t="str">
         <x:v>My Dignity Restored Shelter for the Abused Women and Children</x:v>
       </x:c>
-      <x:c r="C6" s="5" t="str">
+      <x:c r="C6" s="6" t="str">
         <x:v>Free State</x:v>
       </x:c>
-      <x:c r="D6" s="5" t="str">
+      <x:c r="D6" s="6" t="str">
         <x:v>Lefikeng Secondary School</x:v>
       </x:c>
-      <x:c r="E6" s="7" t="n">
+      <x:c r="E6" s="8" t="n">
         <x:v>1.878</x:v>
       </x:c>
-      <x:c r="F6" s="7" t="n">
+      <x:c r="F6" s="8" t="n">
         <x:v>2.811</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="42" customHeight="1">
-      <x:c r="A7" s="5" t="str">
+    <x:row r="7" ht="15" customHeight="1">
+      <x:c r="A7" s="6" t="str">
         <x:v>Free State</x:v>
       </x:c>
-      <x:c r="B7" s="5" t="str">
+      <x:c r="B7" s="6" t="str">
         <x:v>My Dignity Restored Shelter for the Abused Women and Children</x:v>
       </x:c>
-      <x:c r="C7" s="5" t="str">
+      <x:c r="C7" s="6" t="str">
         <x:v>Free State</x:v>
       </x:c>
-      <x:c r="D7" s="5" t="str">
+      <x:c r="D7" s="6" t="str">
         <x:v>Kgorathuto Secondary School</x:v>
       </x:c>
-      <x:c r="E7" s="7" t="n">
+      <x:c r="E7" s="8" t="n">
         <x:v>5.767</x:v>
       </x:c>
-      <x:c r="F7" s="7" t="n">
+      <x:c r="F7" s="8" t="n">
         <x:v>7.59</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="42" customHeight="1">
-      <x:c r="A8" s="5" t="str">
-        <x:v>Gauteng</x:v>
-      </x:c>
-      <x:c r="B8" s="5" t="str">
+    <x:row r="8" ht="15" customHeight="1">
+      <x:c r="A8" s="6" t="str">
+        <x:v>Gauteng</x:v>
+      </x:c>
+      <x:c r="B8" s="6" t="str">
         <x:v>Eldorado Park Family Crisis Centre</x:v>
       </x:c>
-      <x:c r="C8" s="5" t="str">
-        <x:v>Gauteng</x:v>
-      </x:c>
-      <x:c r="D8" s="5" t="str">
+      <x:c r="C8" s="6" t="str">
+        <x:v>Gauteng</x:v>
+      </x:c>
+      <x:c r="D8" s="6" t="str">
         <x:v>Heerengracht Primary School</x:v>
       </x:c>
-      <x:c r="E8" s="7" t="n">
+      <x:c r="E8" s="8" t="n">
         <x:v>1.924</x:v>
       </x:c>
-      <x:c r="F8" s="7" t="n">
+      <x:c r="F8" s="8" t="n">
         <x:v>2.879</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="42" customHeight="1">
-      <x:c r="A9" s="5" t="str">
-        <x:v>Gauteng</x:v>
-      </x:c>
-      <x:c r="B9" s="5" t="str">
+    <x:row r="9" ht="15" customHeight="1">
+      <x:c r="A9" s="6" t="str">
+        <x:v>Gauteng</x:v>
+      </x:c>
+      <x:c r="B9" s="6" t="str">
         <x:v>Eldorado Park Family Crisis Centre</x:v>
       </x:c>
-      <x:c r="C9" s="5" t="str">
-        <x:v>Gauteng</x:v>
-      </x:c>
-      <x:c r="D9" s="5" t="str">
+      <x:c r="C9" s="6" t="str">
+        <x:v>Gauteng</x:v>
+      </x:c>
+      <x:c r="D9" s="6" t="str">
         <x:v>Eldomaine High School</x:v>
       </x:c>
-      <x:c r="E9" s="7" t="n">
+      <x:c r="E9" s="8" t="n">
         <x:v>1.274</x:v>
       </x:c>
-      <x:c r="F9" s="7" t="n">
+      <x:c r="F9" s="8" t="n">
         <x:v>1.695</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="42" customHeight="1">
-      <x:c r="A10" s="5" t="str">
-        <x:v>Gauteng</x:v>
-      </x:c>
-      <x:c r="B10" s="5" t="str">
+    <x:row r="10" ht="15" customHeight="1">
+      <x:c r="A10" s="6" t="str">
+        <x:v>Gauteng</x:v>
+      </x:c>
+      <x:c r="B10" s="6" t="str">
         <x:v>Eldorado Park Family Crisis Centre</x:v>
       </x:c>
-      <x:c r="C10" s="5" t="str">
-        <x:v>Gauteng</x:v>
-      </x:c>
-      <x:c r="D10" s="5" t="str">
+      <x:c r="C10" s="6" t="str">
+        <x:v>Gauteng</x:v>
+      </x:c>
+      <x:c r="D10" s="6" t="str">
         <x:v>Eldorado Park Secondary School</x:v>
       </x:c>
-      <x:c r="E10" s="7" t="n">
+      <x:c r="E10" s="8" t="n">
         <x:v>0.593</x:v>
       </x:c>
-      <x:c r="F10" s="7" t="n">
+      <x:c r="F10" s="8" t="n">
         <x:v>1.851</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="42" customHeight="1">
-      <x:c r="A11" s="5" t="str">
-        <x:v>Gauteng</x:v>
-      </x:c>
-      <x:c r="B11" s="5" t="str">
+    <x:row r="11" ht="15" customHeight="1">
+      <x:c r="A11" s="6" t="str">
+        <x:v>Gauteng</x:v>
+      </x:c>
+      <x:c r="B11" s="6" t="str">
         <x:v>Vanderbijlpark Trauma Counselling Empowerment Centre</x:v>
       </x:c>
-      <x:c r="C11" s="5" t="str">
-        <x:v>Gauteng</x:v>
-      </x:c>
-      <x:c r="D11" s="5" t="str">
+      <x:c r="C11" s="6" t="str">
+        <x:v>Gauteng</x:v>
+      </x:c>
+      <x:c r="D11" s="6" t="str">
         <x:v>Dr Molefi Oliphant High School of Specialization</x:v>
       </x:c>
-      <x:c r="E11" s="7" t="n">
+      <x:c r="E11" s="8" t="n">
         <x:v>0.511</x:v>
       </x:c>
-      <x:c r="F11" s="7" t="n">
+      <x:c r="F11" s="8" t="n">
         <x:v>1.044</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="42" customHeight="1">
-      <x:c r="A12" s="5" t="str">
-        <x:v>Gauteng</x:v>
-      </x:c>
-      <x:c r="B12" s="5" t="str">
+    <x:row r="12" ht="15" customHeight="1">
+      <x:c r="A12" s="6" t="str">
+        <x:v>Gauteng</x:v>
+      </x:c>
+      <x:c r="B12" s="6" t="str">
         <x:v>Vanderbijlpark Trauma Counselling Empowerment Centre</x:v>
       </x:c>
-      <x:c r="C12" s="5" t="str">
-        <x:v>Gauteng</x:v>
-      </x:c>
-      <x:c r="D12" s="5" t="str">
+      <x:c r="C12" s="6" t="str">
+        <x:v>Gauteng</x:v>
+      </x:c>
+      <x:c r="D12" s="6" t="str">
         <x:v>Ikokobetseng Primary School</x:v>
       </x:c>
-      <x:c r="E12" s="7" t="n">
+      <x:c r="E12" s="8" t="n">
         <x:v>0.41</x:v>
       </x:c>
-      <x:c r="F12" s="7" t="n">
+      <x:c r="F12" s="8" t="n">
         <x:v>1.274</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="42" customHeight="1">
-      <x:c r="A13" s="5" t="str">
-        <x:v>Gauteng</x:v>
-      </x:c>
-      <x:c r="B13" s="5" t="str">
+    <x:row r="13" ht="15" customHeight="1">
+      <x:c r="A13" s="6" t="str">
+        <x:v>Gauteng</x:v>
+      </x:c>
+      <x:c r="B13" s="6" t="str">
         <x:v>Vanderbijlpark Trauma Counselling Empowerment Centre</x:v>
       </x:c>
-      <x:c r="C13" s="5" t="str">
-        <x:v>Gauteng</x:v>
-      </x:c>
-      <x:c r="D13" s="5" t="str">
+      <x:c r="C13" s="6" t="str">
+        <x:v>Gauteng</x:v>
+      </x:c>
+      <x:c r="D13" s="6" t="str">
         <x:v>Sapphire Secondary School</x:v>
       </x:c>
-      <x:c r="E13" s="7" t="n">
+      <x:c r="E13" s="8" t="n">
         <x:v>0.783</x:v>
       </x:c>
-      <x:c r="F13" s="7" t="n">
+      <x:c r="F13" s="8" t="n">
         <x:v>1.173</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="42" customHeight="1">
-      <x:c r="A14" s="5" t="str">
-        <x:v>Gauteng</x:v>
-      </x:c>
-      <x:c r="B14" s="5" t="str">
+    <x:row r="14" ht="15" customHeight="1">
+      <x:c r="A14" s="6" t="str">
+        <x:v>Gauteng</x:v>
+      </x:c>
+      <x:c r="B14" s="6" t="str">
         <x:v>Get Informed Youth Development Centre</x:v>
       </x:c>
-      <x:c r="C14" s="5" t="str">
-        <x:v>Gauteng</x:v>
-      </x:c>
-      <x:c r="D14" s="5" t="str">
+      <x:c r="C14" s="6" t="str">
+        <x:v>Gauteng</x:v>
+      </x:c>
+      <x:c r="D14" s="6" t="str">
         <x:v>Phomolong Secondary School</x:v>
       </x:c>
-      <x:c r="E14" s="7" t="n">
+      <x:c r="E14" s="8" t="n">
         <x:v>0.664</x:v>
       </x:c>
-      <x:c r="F14" s="7" t="n">
+      <x:c r="F14" s="8" t="n">
         <x:v>0.752</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="42" customHeight="1">
-      <x:c r="A15" s="5" t="str">
-        <x:v>Gauteng</x:v>
-      </x:c>
-      <x:c r="B15" s="5" t="str">
+    <x:row r="15" ht="15" customHeight="1">
+      <x:c r="A15" s="6" t="str">
+        <x:v>Gauteng</x:v>
+      </x:c>
+      <x:c r="B15" s="6" t="str">
         <x:v>Get Informed Youth Development Centre</x:v>
       </x:c>
-      <x:c r="C15" s="5" t="str">
-        <x:v>Gauteng</x:v>
-      </x:c>
-      <x:c r="D15" s="5" t="str">
+      <x:c r="C15" s="6" t="str">
+        <x:v>Gauteng</x:v>
+      </x:c>
+      <x:c r="D15" s="6" t="str">
         <x:v>Ikusasa Comprehensive High School</x:v>
       </x:c>
-      <x:c r="E15" s="7" t="n">
+      <x:c r="E15" s="8" t="n">
         <x:v>7.039</x:v>
       </x:c>
-      <x:c r="F15" s="7" t="n">
+      <x:c r="F15" s="8" t="n">
         <x:v>10.066</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="42" customHeight="1">
-      <x:c r="A16" s="5" t="str">
-        <x:v>Gauteng</x:v>
-      </x:c>
-      <x:c r="B16" s="5" t="str">
+    <x:row r="16" ht="15" customHeight="1">
+      <x:c r="A16" s="6" t="str">
+        <x:v>Gauteng</x:v>
+      </x:c>
+      <x:c r="B16" s="6" t="str">
         <x:v>Get Informed Youth Development Centre</x:v>
       </x:c>
-      <x:c r="C16" s="5" t="str">
-        <x:v>Gauteng</x:v>
-      </x:c>
-      <x:c r="D16" s="5" t="str">
+      <x:c r="C16" s="6" t="str">
+        <x:v>Gauteng</x:v>
+      </x:c>
+      <x:c r="D16" s="6" t="str">
         <x:v>Shukumani Primary School</x:v>
       </x:c>
-      <x:c r="E16" s="7" t="n">
+      <x:c r="E16" s="8" t="n">
         <x:v>7.291</x:v>
       </x:c>
-      <x:c r="F16" s="7" t="n">
+      <x:c r="F16" s="8" t="n">
         <x:v>9.272</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="42" customHeight="1">
-      <x:c r="A17" s="5" t="str">
-        <x:v>Gauteng</x:v>
-      </x:c>
-      <x:c r="B17" s="5" t="str">
+    <x:row r="17" ht="15" customHeight="1">
+      <x:c r="A17" s="6" t="str">
+        <x:v>Gauteng</x:v>
+      </x:c>
+      <x:c r="B17" s="6" t="str">
         <x:v>Rekopane Drop-In Centre</x:v>
       </x:c>
-      <x:c r="C17" s="5" t="str">
-        <x:v>Gauteng</x:v>
-      </x:c>
-      <x:c r="D17" s="5" t="str">
+      <x:c r="C17" s="6" t="str">
+        <x:v>Gauteng</x:v>
+      </x:c>
+      <x:c r="D17" s="6" t="str">
         <x:v>Pro-Practicum Vocational School</x:v>
       </x:c>
-      <x:c r="E17" s="7" t="n">
+      <x:c r="E17" s="8" t="n">
         <x:v>2.718</x:v>
       </x:c>
-      <x:c r="F17" s="7" t="n">
+      <x:c r="F17" s="8" t="n">
         <x:v>3.314</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="42" customHeight="1">
-      <x:c r="A18" s="5" t="str">
-        <x:v>Gauteng</x:v>
-      </x:c>
-      <x:c r="B18" s="5" t="str">
+    <x:row r="18" ht="15" customHeight="1">
+      <x:c r="A18" s="6" t="str">
+        <x:v>Gauteng</x:v>
+      </x:c>
+      <x:c r="B18" s="6" t="str">
         <x:v>Rekopane Drop-In Centre</x:v>
       </x:c>
-      <x:c r="C18" s="5" t="str">
-        <x:v>Gauteng</x:v>
-      </x:c>
-      <x:c r="D18" s="5" t="str">
+      <x:c r="C18" s="6" t="str">
+        <x:v>Gauteng</x:v>
+      </x:c>
+      <x:c r="D18" s="6" t="str">
         <x:v>West Rand Mine Primary School</x:v>
       </x:c>
-      <x:c r="E18" s="7" t="n">
+      <x:c r="E18" s="8" t="n">
         <x:v>3.257</x:v>
       </x:c>
-      <x:c r="F18" s="7" t="n">
+      <x:c r="F18" s="8" t="n">
         <x:v>5.046</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="42" customHeight="1">
-      <x:c r="A19" s="5" t="str">
-        <x:v>Gauteng</x:v>
-      </x:c>
-      <x:c r="B19" s="5" t="str">
+    <x:row r="19" ht="15" customHeight="1">
+      <x:c r="A19" s="6" t="str">
+        <x:v>Gauteng</x:v>
+      </x:c>
+      <x:c r="B19" s="6" t="str">
         <x:v>Rekopane Drop-In Centre</x:v>
       </x:c>
-      <x:c r="C19" s="5" t="str">
-        <x:v>Gauteng</x:v>
-      </x:c>
-      <x:c r="D19" s="5" t="str">
+      <x:c r="C19" s="6" t="str">
+        <x:v>Gauteng</x:v>
+      </x:c>
+      <x:c r="D19" s="6" t="str">
         <x:v>Jan de Klerk High School</x:v>
       </x:c>
-      <x:c r="E19" s="7" t="n">
+      <x:c r="E19" s="8" t="n">
         <x:v>1.157</x:v>
       </x:c>
-      <x:c r="F19" s="7" t="n">
+      <x:c r="F19" s="8" t="n">
         <x:v>1.423</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="42" customHeight="1">
-      <x:c r="A20" s="5" t="str">
-        <x:v>Gauteng</x:v>
-      </x:c>
-      <x:c r="B20" s="5" t="str">
+    <x:row r="20" ht="15" customHeight="1">
+      <x:c r="A20" s="6" t="str">
+        <x:v>Gauteng</x:v>
+      </x:c>
+      <x:c r="B20" s="6" t="str">
         <x:v>OUT-LGBT Well-being</x:v>
       </x:c>
-      <x:c r="C20" s="5" t="str">
-        <x:v>Gauteng</x:v>
-      </x:c>
-      <x:c r="D20" s="5" t="str">
+      <x:c r="C20" s="6" t="str">
+        <x:v>Gauteng</x:v>
+      </x:c>
+      <x:c r="D20" s="6" t="str">
         <x:v>Dr WF Nkomo High School</x:v>
       </x:c>
-      <x:c r="E20" s="7" t="n">
+      <x:c r="E20" s="8" t="n">
         <x:v>18.133</x:v>
       </x:c>
-      <x:c r="F20" s="7" t="n">
+      <x:c r="F20" s="8" t="n">
         <x:v>21.126</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" ht="42" customHeight="1">
-      <x:c r="A21" s="5" t="str">
-        <x:v>Gauteng</x:v>
-      </x:c>
-      <x:c r="B21" s="5" t="str">
+    <x:row r="21" ht="15" customHeight="1">
+      <x:c r="A21" s="6" t="str">
+        <x:v>Gauteng</x:v>
+      </x:c>
+      <x:c r="B21" s="6" t="str">
         <x:v>OUT-LGBT Well-being</x:v>
       </x:c>
-      <x:c r="C21" s="5" t="str">
-        <x:v>Gauteng</x:v>
-      </x:c>
-      <x:c r="D21" s="5" t="str">
+      <x:c r="C21" s="6" t="str">
+        <x:v>Gauteng</x:v>
+      </x:c>
+      <x:c r="D21" s="6" t="str">
         <x:v>Olievenhoutbosch Secondary School</x:v>
       </x:c>
-      <x:c r="E21" s="7" t="n">
+      <x:c r="E21" s="8" t="n">
         <x:v>24.296</x:v>
       </x:c>
-      <x:c r="F21" s="7" t="n">
+      <x:c r="F21" s="8" t="n">
         <x:v>30.304</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="42" customHeight="1">
-      <x:c r="A22" s="5" t="str">
-        <x:v>Gauteng</x:v>
-      </x:c>
-      <x:c r="B22" s="5" t="str">
+    <x:row r="22" ht="15" customHeight="1">
+      <x:c r="A22" s="6" t="str">
+        <x:v>Gauteng</x:v>
+      </x:c>
+      <x:c r="B22" s="6" t="str">
         <x:v>OUT-LGBT Well-being</x:v>
       </x:c>
-      <x:c r="C22" s="5" t="str">
-        <x:v>Gauteng</x:v>
-      </x:c>
-      <x:c r="D22" s="5" t="str">
+      <x:c r="C22" s="6" t="str">
+        <x:v>Gauteng</x:v>
+      </x:c>
+      <x:c r="D22" s="6" t="str">
         <x:v>Hofmeyr High School</x:v>
       </x:c>
-      <x:c r="E22" s="7" t="n">
+      <x:c r="E22" s="8" t="n">
         <x:v>18.137</x:v>
       </x:c>
-      <x:c r="F22" s="7" t="n">
+      <x:c r="F22" s="8" t="n">
         <x:v>21.994</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" ht="42" customHeight="1">
-      <x:c r="A23" s="5" t="str">
-        <x:v>KwaZulu-Natal</x:v>
-      </x:c>
-      <x:c r="B23" s="5" t="str">
+    <x:row r="23" ht="15" customHeight="1">
+      <x:c r="A23" s="6" t="str">
+        <x:v>KwaZulu-Natal</x:v>
+      </x:c>
+      <x:c r="B23" s="6" t="str">
         <x:v>Community HealthCare Solutions</x:v>
       </x:c>
-      <x:c r="C23" s="5" t="str">
-        <x:v>KwaZulu-Natal</x:v>
-      </x:c>
-      <x:c r="D23" s="5" t="str">
+      <x:c r="C23" s="6" t="str">
+        <x:v>KwaZulu-Natal</x:v>
+      </x:c>
+      <x:c r="D23" s="6" t="str">
         <x:v>Injoloba Secondary School</x:v>
       </x:c>
-      <x:c r="E23" s="7" t="n">
+      <x:c r="E23" s="8" t="n">
         <x:v>0.163</x:v>
       </x:c>
-      <x:c r="F23" s="7" t="n">
+      <x:c r="F23" s="8" t="n">
         <x:v>0.193</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" ht="42" customHeight="1">
-      <x:c r="A24" s="5" t="str">
-        <x:v>KwaZulu-Natal</x:v>
-      </x:c>
-      <x:c r="B24" s="5" t="str">
+    <x:row r="24" ht="15" customHeight="1">
+      <x:c r="A24" s="6" t="str">
+        <x:v>KwaZulu-Natal</x:v>
+      </x:c>
+      <x:c r="B24" s="6" t="str">
         <x:v>Community HealthCare Solutions</x:v>
       </x:c>
-      <x:c r="C24" s="5" t="str">
-        <x:v>KwaZulu-Natal</x:v>
-      </x:c>
-      <x:c r="D24" s="5" t="str">
+      <x:c r="C24" s="6" t="str">
+        <x:v>KwaZulu-Natal</x:v>
+      </x:c>
+      <x:c r="D24" s="6" t="str">
         <x:v>Nogqaza Primary School</x:v>
       </x:c>
-      <x:c r="E24" s="7" t="n">
+      <x:c r="E24" s="8" t="n">
         <x:v>0.337</x:v>
       </x:c>
-      <x:c r="F24" s="7" t="n">
+      <x:c r="F24" s="8" t="n">
         <x:v>0.394</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" ht="42" customHeight="1">
-      <x:c r="A25" s="5" t="str">
-        <x:v>KwaZulu-Natal</x:v>
-      </x:c>
-      <x:c r="B25" s="5" t="str">
+    <x:row r="25" ht="15" customHeight="1">
+      <x:c r="A25" s="6" t="str">
+        <x:v>KwaZulu-Natal</x:v>
+      </x:c>
+      <x:c r="B25" s="6" t="str">
         <x:v>Community HealthCare Solutions</x:v>
       </x:c>
-      <x:c r="C25" s="5" t="str">
-        <x:v>KwaZulu-Natal</x:v>
-      </x:c>
-      <x:c r="D25" s="5" t="str">
+      <x:c r="C25" s="6" t="str">
+        <x:v>KwaZulu-Natal</x:v>
+      </x:c>
+      <x:c r="D25" s="6" t="str">
         <x:v>Howick Secondary</x:v>
       </x:c>
-      <x:c r="E25" s="7" t="n">
+      <x:c r="E25" s="8" t="n">
         <x:v>1.967</x:v>
       </x:c>
-      <x:c r="F25" s="7" t="n">
+      <x:c r="F25" s="8" t="n">
         <x:v>3.872</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" ht="42" customHeight="1">
-      <x:c r="A26" s="5" t="str">
-        <x:v>KwaZulu-Natal</x:v>
-      </x:c>
-      <x:c r="B26" s="5" t="str">
+    <x:row r="26" ht="15" customHeight="1">
+      <x:c r="A26" s="6" t="str">
+        <x:v>KwaZulu-Natal</x:v>
+      </x:c>
+      <x:c r="B26" s="6" t="str">
         <x:v>Lungelo Youth Development</x:v>
       </x:c>
-      <x:c r="C26" s="5" t="str">
-        <x:v>KwaZulu-Natal</x:v>
-      </x:c>
-      <x:c r="D26" s="5" t="str">
+      <x:c r="C26" s="6" t="str">
+        <x:v>KwaZulu-Natal</x:v>
+      </x:c>
+      <x:c r="D26" s="6" t="str">
         <x:v>Emankwathini Primary School</x:v>
       </x:c>
-      <x:c r="E26" s="7" t="n">
+      <x:c r="E26" s="8" t="n">
         <x:v>14.289</x:v>
       </x:c>
-      <x:c r="F26" s="7" t="n">
+      <x:c r="F26" s="8" t="n">
         <x:v>16.95</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" ht="42" customHeight="1">
-      <x:c r="A27" s="5" t="str">
-        <x:v>KwaZulu-Natal</x:v>
-      </x:c>
-      <x:c r="B27" s="5" t="str">
+    <x:row r="27" ht="15" customHeight="1">
+      <x:c r="A27" s="6" t="str">
+        <x:v>KwaZulu-Natal</x:v>
+      </x:c>
+      <x:c r="B27" s="6" t="str">
         <x:v>Lungelo Youth Development</x:v>
       </x:c>
-      <x:c r="C27" s="5" t="str">
-        <x:v>KwaZulu-Natal</x:v>
-      </x:c>
-      <x:c r="D27" s="5" t="str">
+      <x:c r="C27" s="6" t="str">
+        <x:v>KwaZulu-Natal</x:v>
+      </x:c>
+      <x:c r="D27" s="6" t="str">
         <x:v>Ntongande High School</x:v>
       </x:c>
-      <x:c r="E27" s="7" t="n">
+      <x:c r="E27" s="8" t="n">
         <x:v>6.166</x:v>
       </x:c>
-      <x:c r="F27" s="7" t="n">
+      <x:c r="F27" s="8" t="n">
         <x:v>7.214</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" ht="42" customHeight="1">
-      <x:c r="A28" s="5" t="str">
-        <x:v>KwaZulu-Natal</x:v>
-      </x:c>
-      <x:c r="B28" s="5" t="str">
+    <x:row r="28" ht="15" customHeight="1">
+      <x:c r="A28" s="6" t="str">
+        <x:v>KwaZulu-Natal</x:v>
+      </x:c>
+      <x:c r="B28" s="6" t="str">
         <x:v>Lungelo Youth Development</x:v>
       </x:c>
-      <x:c r="C28" s="5" t="str">
-        <x:v>KwaZulu-Natal</x:v>
-      </x:c>
-      <x:c r="D28" s="5" t="str">
+      <x:c r="C28" s="6" t="str">
+        <x:v>KwaZulu-Natal</x:v>
+      </x:c>
+      <x:c r="D28" s="6" t="str">
         <x:v>Nqumizwe High School</x:v>
       </x:c>
-      <x:c r="E28" s="7" t="n">
+      <x:c r="E28" s="8" t="n">
         <x:v>96.911</x:v>
       </x:c>
-      <x:c r="F28" s="7" t="n">
+      <x:c r="F28" s="8" t="n">
         <x:v>136.561</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" ht="42" customHeight="1">
-      <x:c r="A29" s="5" t="str">
-        <x:v>KwaZulu-Natal</x:v>
-      </x:c>
-      <x:c r="B29" s="5" t="str">
+    <x:row r="29" ht="15" customHeight="1">
+      <x:c r="A29" s="6" t="str">
+        <x:v>KwaZulu-Natal</x:v>
+      </x:c>
+      <x:c r="B29" s="6" t="str">
         <x:v>Kwa Zulu-Natal Network On Violence Against Women</x:v>
       </x:c>
-      <x:c r="C29" s="5" t="str">
-        <x:v>KwaZulu-Natal</x:v>
-      </x:c>
-      <x:c r="D29" s="5" t="str">
+      <x:c r="C29" s="6" t="str">
+        <x:v>KwaZulu-Natal</x:v>
+      </x:c>
+      <x:c r="D29" s="6" t="str">
         <x:v>Dumehlezi High School</x:v>
       </x:c>
-      <x:c r="E29" s="7" t="n">
+      <x:c r="E29" s="8" t="n">
         <x:v>18.098</x:v>
       </x:c>
-      <x:c r="F29" s="7" t="n">
+      <x:c r="F29" s="8" t="n">
         <x:v>26.314</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" ht="42" customHeight="1">
-      <x:c r="A30" s="5" t="str">
-        <x:v>KwaZulu-Natal</x:v>
-      </x:c>
-      <x:c r="B30" s="5" t="str">
+    <x:row r="30" ht="15" customHeight="1">
+      <x:c r="A30" s="6" t="str">
+        <x:v>KwaZulu-Natal</x:v>
+      </x:c>
+      <x:c r="B30" s="6" t="str">
         <x:v>Kwa Zulu-Natal Network On Violence Against Women</x:v>
       </x:c>
-      <x:c r="C30" s="5" t="str">
-        <x:v>KwaZulu-Natal</x:v>
-      </x:c>
-      <x:c r="D30" s="5" t="str">
+      <x:c r="C30" s="6" t="str">
+        <x:v>KwaZulu-Natal</x:v>
+      </x:c>
+      <x:c r="D30" s="6" t="str">
         <x:v>Ekwazini High School</x:v>
       </x:c>
-      <x:c r="E30" s="7" t="n">
+      <x:c r="E30" s="8" t="n">
         <x:v>17.592</x:v>
       </x:c>
-      <x:c r="F30" s="7" t="n">
+      <x:c r="F30" s="8" t="n">
         <x:v>23.916</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" ht="42" customHeight="1">
-      <x:c r="A31" s="5" t="str">
-        <x:v>KwaZulu-Natal</x:v>
-      </x:c>
-      <x:c r="B31" s="5" t="str">
+    <x:row r="31" ht="15" customHeight="1">
+      <x:c r="A31" s="6" t="str">
+        <x:v>KwaZulu-Natal</x:v>
+      </x:c>
+      <x:c r="B31" s="6" t="str">
         <x:v>Kwa Zulu-Natal Network On Violence Against Women</x:v>
       </x:c>
-      <x:c r="C31" s="5" t="str">
-        <x:v>KwaZulu-Natal</x:v>
-      </x:c>
-      <x:c r="D31" s="5" t="str">
+      <x:c r="C31" s="6" t="str">
+        <x:v>KwaZulu-Natal</x:v>
+      </x:c>
+      <x:c r="D31" s="6" t="str">
         <x:v>Ntuzuma Junior Primary School</x:v>
       </x:c>
-      <x:c r="E31" s="7" t="n">
+      <x:c r="E31" s="8" t="n">
         <x:v>17.892</x:v>
       </x:c>
-      <x:c r="F31" s="7" t="n">
+      <x:c r="F31" s="8" t="n">
         <x:v>25.667</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" ht="42" customHeight="1">
-      <x:c r="A32" s="5" t="str">
-        <x:v>KwaZulu-Natal</x:v>
-      </x:c>
-      <x:c r="B32" s="5" t="str">
+    <x:row r="32" ht="15" customHeight="1">
+      <x:c r="A32" s="6" t="str">
+        <x:v>KwaZulu-Natal</x:v>
+      </x:c>
+      <x:c r="B32" s="6" t="str">
         <x:v>Woza Moya Community Development Project NPC</x:v>
       </x:c>
-      <x:c r="C32" s="5" t="str">
-        <x:v>KwaZulu-Natal</x:v>
-      </x:c>
-      <x:c r="D32" s="5" t="str">
+      <x:c r="C32" s="6" t="str">
+        <x:v>KwaZulu-Natal</x:v>
+      </x:c>
+      <x:c r="D32" s="6" t="str">
         <x:v>Mavanagane High School</x:v>
       </x:c>
-      <x:c r="E32" s="7" t="n">
+      <x:c r="E32" s="8" t="n">
         <x:v>3.414</x:v>
       </x:c>
-      <x:c r="F32" s="7" t="n">
+      <x:c r="F32" s="8" t="n">
         <x:v>6.933</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" ht="42" customHeight="1">
-      <x:c r="A33" s="5" t="str">
-        <x:v>KwaZulu-Natal</x:v>
-      </x:c>
-      <x:c r="B33" s="5" t="str">
+    <x:row r="33" ht="15" customHeight="1">
+      <x:c r="A33" s="6" t="str">
+        <x:v>KwaZulu-Natal</x:v>
+      </x:c>
+      <x:c r="B33" s="6" t="str">
         <x:v>Woza Moya Community Development Project NPC</x:v>
       </x:c>
-      <x:c r="C33" s="5" t="str">
-        <x:v>KwaZulu-Natal</x:v>
-      </x:c>
-      <x:c r="D33" s="5" t="str">
+      <x:c r="C33" s="6" t="str">
+        <x:v>KwaZulu-Natal</x:v>
+      </x:c>
+      <x:c r="D33" s="6" t="str">
         <x:v>Sinevuso High School</x:v>
       </x:c>
-      <x:c r="E33" s="7" t="n">
+      <x:c r="E33" s="8" t="n">
         <x:v>0.604</x:v>
       </x:c>
-      <x:c r="F33" s="7" t="n">
+      <x:c r="F33" s="8" t="n">
         <x:v>0.737</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" ht="42" customHeight="1">
-      <x:c r="A34" s="5" t="str">
-        <x:v>KwaZulu-Natal</x:v>
-      </x:c>
-      <x:c r="B34" s="5" t="str">
+    <x:row r="34" ht="15" customHeight="1">
+      <x:c r="A34" s="6" t="str">
+        <x:v>KwaZulu-Natal</x:v>
+      </x:c>
+      <x:c r="B34" s="6" t="str">
         <x:v>Woza Moya Community Development Project NPC</x:v>
       </x:c>
-      <x:c r="C34" s="5" t="str">
-        <x:v>KwaZulu-Natal</x:v>
-      </x:c>
-      <x:c r="D34" s="5" t="str">
+      <x:c r="C34" s="6" t="str">
+        <x:v>KwaZulu-Natal</x:v>
+      </x:c>
+      <x:c r="D34" s="6" t="str">
         <x:v>Mpofini Primary School</x:v>
       </x:c>
-      <x:c r="E34" s="7" t="n">
+      <x:c r="E34" s="8" t="n">
         <x:v>9.558</x:v>
       </x:c>
-      <x:c r="F34" s="7" t="n">
+      <x:c r="F34" s="8" t="n">
         <x:v>16.264</x:v>
       </x:c>
     </x:row>
-    <x:row r="35" ht="42" customHeight="1">
-      <x:c r="A35" s="5" t="str">
-        <x:v>KwaZulu-Natal</x:v>
-      </x:c>
-      <x:c r="B35" s="5" t="str">
+    <x:row r="35" ht="15" customHeight="1">
+      <x:c r="A35" s="6" t="str">
+        <x:v>KwaZulu-Natal</x:v>
+      </x:c>
+      <x:c r="B35" s="6" t="str">
         <x:v>Families South Africa Pietermaritzburg</x:v>
       </x:c>
-      <x:c r="C35" s="5" t="str">
-        <x:v>KwaZulu-Natal</x:v>
-      </x:c>
-      <x:c r="D35" s="5" t="str">
+      <x:c r="C35" s="6" t="str">
+        <x:v>KwaZulu-Natal</x:v>
+      </x:c>
+      <x:c r="D35" s="6" t="str">
         <x:v>Mbambangalo High School</x:v>
       </x:c>
-      <x:c r="E35" s="7" t="n">
+      <x:c r="E35" s="8" t="n">
         <x:v>17.887</x:v>
       </x:c>
-      <x:c r="F35" s="7" t="n">
+      <x:c r="F35" s="8" t="n">
         <x:v>23.605</x:v>
       </x:c>
     </x:row>
-    <x:row r="36" ht="42" customHeight="1">
-      <x:c r="A36" s="5" t="str">
-        <x:v>KwaZulu-Natal</x:v>
-      </x:c>
-      <x:c r="B36" s="5" t="str">
+    <x:row r="36" ht="15" customHeight="1">
+      <x:c r="A36" s="6" t="str">
+        <x:v>KwaZulu-Natal</x:v>
+      </x:c>
+      <x:c r="B36" s="6" t="str">
         <x:v>Families South Africa Pietermaritzburg</x:v>
       </x:c>
-      <x:c r="C36" s="5" t="str">
-        <x:v>KwaZulu-Natal</x:v>
-      </x:c>
-      <x:c r="D36" s="5" t="str">
+      <x:c r="C36" s="6" t="str">
+        <x:v>KwaZulu-Natal</x:v>
+      </x:c>
+      <x:c r="D36" s="6" t="str">
         <x:v>Laduma High School</x:v>
       </x:c>
-      <x:c r="E36" s="7" t="n">
+      <x:c r="E36" s="8" t="n">
         <x:v>6.169</x:v>
       </x:c>
-      <x:c r="F36" s="7" t="n">
+      <x:c r="F36" s="8" t="n">
         <x:v>7.613</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" ht="42" customHeight="1">
-      <x:c r="A37" s="5" t="str">
-        <x:v>KwaZulu-Natal</x:v>
-      </x:c>
-      <x:c r="B37" s="5" t="str">
+    <x:row r="37" ht="15" customHeight="1">
+      <x:c r="A37" s="6" t="str">
+        <x:v>KwaZulu-Natal</x:v>
+      </x:c>
+      <x:c r="B37" s="6" t="str">
         <x:v>Families South Africa Pietermaritzburg</x:v>
       </x:c>
-      <x:c r="C37" s="5" t="str">
-        <x:v>KwaZulu-Natal</x:v>
-      </x:c>
-      <x:c r="D37" s="5" t="str">
+      <x:c r="C37" s="6" t="str">
+        <x:v>KwaZulu-Natal</x:v>
+      </x:c>
+      <x:c r="D37" s="6" t="str">
         <x:v>Esigodini Primary School</x:v>
       </x:c>
-      <x:c r="E37" s="7" t="n">
+      <x:c r="E37" s="8" t="n">
         <x:v>11.562</x:v>
       </x:c>
-      <x:c r="F37" s="7" t="n">
+      <x:c r="F37" s="8" t="n">
         <x:v>14.775</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" ht="42" customHeight="1">
-      <x:c r="A38" s="5" t="str">
-        <x:v>Limpopo</x:v>
-      </x:c>
-      <x:c r="B38" s="5" t="str">
+    <x:row r="38" ht="15" customHeight="1">
+      <x:c r="A38" s="6" t="str">
+        <x:v>Limpopo</x:v>
+      </x:c>
+      <x:c r="B38" s="6" t="str">
         <x:v>Limpopo Mental Health Society</x:v>
       </x:c>
-      <x:c r="C38" s="5" t="str">
-        <x:v>Limpopo</x:v>
-      </x:c>
-      <x:c r="D38" s="5" t="str">
+      <x:c r="C38" s="6" t="str">
+        <x:v>Limpopo</x:v>
+      </x:c>
+      <x:c r="D38" s="6" t="str">
         <x:v>Hudson Ntswanwisi High School</x:v>
       </x:c>
-      <x:c r="E38" s="7" t="n">
+      <x:c r="E38" s="8" t="n">
         <x:v>14.681</x:v>
       </x:c>
-      <x:c r="F38" s="7" t="n">
+      <x:c r="F38" s="8" t="n">
         <x:v>18.455</x:v>
       </x:c>
     </x:row>
-    <x:row r="39" ht="42" customHeight="1">
-      <x:c r="A39" s="5" t="str">
-        <x:v>Limpopo</x:v>
-      </x:c>
-      <x:c r="B39" s="5" t="str">
+    <x:row r="39" ht="15" customHeight="1">
+      <x:c r="A39" s="6" t="str">
+        <x:v>Limpopo</x:v>
+      </x:c>
+      <x:c r="B39" s="6" t="str">
         <x:v>Limpopo Mental Health Society</x:v>
       </x:c>
-      <x:c r="C39" s="5" t="str">
-        <x:v>Limpopo</x:v>
-      </x:c>
-      <x:c r="D39" s="5" t="str">
+      <x:c r="C39" s="6" t="str">
+        <x:v>Limpopo</x:v>
+      </x:c>
+      <x:c r="D39" s="6" t="str">
         <x:v>Pherehla-Maake Secondary</x:v>
       </x:c>
-      <x:c r="E39" s="7" t="n">
+      <x:c r="E39" s="8" t="n">
         <x:v>24.296</x:v>
       </x:c>
-      <x:c r="F39" s="7" t="n">
+      <x:c r="F39" s="8" t="n">
         <x:v>29.747</x:v>
       </x:c>
     </x:row>
-    <x:row r="40" ht="42" customHeight="1">
-      <x:c r="A40" s="5" t="str">
-        <x:v>Limpopo</x:v>
-      </x:c>
-      <x:c r="B40" s="5" t="str">
+    <x:row r="40" ht="15" customHeight="1">
+      <x:c r="A40" s="6" t="str">
+        <x:v>Limpopo</x:v>
+      </x:c>
+      <x:c r="B40" s="6" t="str">
         <x:v>Limpopo Mental Health Society</x:v>
       </x:c>
-      <x:c r="C40" s="5" t="str">
-        <x:v>Limpopo</x:v>
-      </x:c>
-      <x:c r="D40" s="5" t="str">
+      <x:c r="C40" s="6" t="str">
+        <x:v>Limpopo</x:v>
+      </x:c>
+      <x:c r="D40" s="6" t="str">
         <x:v>Phusela High School</x:v>
       </x:c>
-      <x:c r="E40" s="7" t="n">
+      <x:c r="E40" s="8" t="n">
         <x:v>19.296</x:v>
       </x:c>
-      <x:c r="F40" s="7" t="n">
+      <x:c r="F40" s="8" t="n">
         <x:v>24.391</x:v>
       </x:c>
     </x:row>
-    <x:row r="41" ht="42" customHeight="1">
-      <x:c r="A41" s="5" t="str">
-        <x:v>Limpopo</x:v>
-      </x:c>
-      <x:c r="B41" s="5" t="str">
+    <x:row r="41" ht="15" customHeight="1">
+      <x:c r="A41" s="6" t="str">
+        <x:v>Limpopo</x:v>
+      </x:c>
+      <x:c r="B41" s="6" t="str">
         <x:v>Broadway Legacy Foundation</x:v>
       </x:c>
-      <x:c r="C41" s="5" t="str">
-        <x:v>Limpopo</x:v>
-      </x:c>
-      <x:c r="D41" s="5" t="str">
+      <x:c r="C41" s="6" t="str">
+        <x:v>Limpopo</x:v>
+      </x:c>
+      <x:c r="D41" s="6" t="str">
         <x:v>Aquaville Combined Primary School</x:v>
       </x:c>
-      <x:c r="E41" s="7" t="n">
+      <x:c r="E41" s="8" t="n">
         <x:v>5.565</x:v>
       </x:c>
-      <x:c r="F41" s="7" t="n">
+      <x:c r="F41" s="8" t="n">
         <x:v>6.733</x:v>
       </x:c>
     </x:row>
-    <x:row r="42" ht="42" customHeight="1">
-      <x:c r="A42" s="5" t="str">
-        <x:v>Limpopo</x:v>
-      </x:c>
-      <x:c r="B42" s="5" t="str">
+    <x:row r="42" ht="15" customHeight="1">
+      <x:c r="A42" s="6" t="str">
+        <x:v>Limpopo</x:v>
+      </x:c>
+      <x:c r="B42" s="6" t="str">
         <x:v>Broadway Legacy Foundation</x:v>
       </x:c>
-      <x:c r="C42" s="5" t="str">
-        <x:v>Limpopo</x:v>
-      </x:c>
-      <x:c r="D42" s="5" t="str">
+      <x:c r="C42" s="6" t="str">
+        <x:v>Limpopo</x:v>
+      </x:c>
+      <x:c r="D42" s="6" t="str">
         <x:v>Moosrivier Combined Primary School</x:v>
       </x:c>
-      <x:c r="E42" s="7" t="n">
+      <x:c r="E42" s="8" t="n">
         <x:v>14.889</x:v>
       </x:c>
-      <x:c r="F42" s="7" t="n">
+      <x:c r="F42" s="8" t="n">
         <x:v>16.104</x:v>
       </x:c>
     </x:row>
-    <x:row r="43" ht="42" customHeight="1">
-      <x:c r="A43" s="5" t="str">
-        <x:v>Limpopo</x:v>
-      </x:c>
-      <x:c r="B43" s="5" t="str">
+    <x:row r="43" ht="15" customHeight="1">
+      <x:c r="A43" s="6" t="str">
+        <x:v>Limpopo</x:v>
+      </x:c>
+      <x:c r="B43" s="6" t="str">
         <x:v>Broadway Legacy Foundation</x:v>
       </x:c>
-      <x:c r="C43" s="5" t="str">
-        <x:v>Limpopo</x:v>
-      </x:c>
-      <x:c r="D43" s="5" t="str">
+      <x:c r="C43" s="6" t="str">
+        <x:v>Limpopo</x:v>
+      </x:c>
+      <x:c r="D43" s="6" t="str">
         <x:v>Rakediwane High School</x:v>
       </x:c>
-      <x:c r="E43" s="7" t="n">
+      <x:c r="E43" s="8" t="n">
         <x:v>3.956</x:v>
       </x:c>
-      <x:c r="F43" s="7" t="n">
+      <x:c r="F43" s="8" t="n">
         <x:v>4.204</x:v>
       </x:c>
     </x:row>
-    <x:row r="44" ht="42" customHeight="1">
-      <x:c r="A44" s="5" t="str">
-        <x:v>Limpopo</x:v>
-      </x:c>
-      <x:c r="B44" s="5" t="str">
+    <x:row r="44" ht="15" customHeight="1">
+      <x:c r="A44" s="6" t="str">
+        <x:v>Limpopo</x:v>
+      </x:c>
+      <x:c r="B44" s="6" t="str">
         <x:v>Northam Victim Empowerment</x:v>
       </x:c>
-      <x:c r="C44" s="5" t="str">
-        <x:v>Limpopo</x:v>
-      </x:c>
-      <x:c r="D44" s="5" t="str">
+      <x:c r="C44" s="6" t="str">
+        <x:v>Limpopo</x:v>
+      </x:c>
+      <x:c r="D44" s="6" t="str">
         <x:v>Chromine Primary School</x:v>
       </x:c>
-      <x:c r="E44" s="7" t="n">
+      <x:c r="E44" s="8" t="n">
         <x:v>195.604</x:v>
       </x:c>
-      <x:c r="F44" s="7" t="n">
+      <x:c r="F44" s="8" t="n">
         <x:v>282.779</x:v>
       </x:c>
     </x:row>
-    <x:row r="45" ht="42" customHeight="1">
-      <x:c r="A45" s="5" t="str">
-        <x:v>Limpopo</x:v>
-      </x:c>
-      <x:c r="B45" s="5" t="str">
+    <x:row r="45" ht="15" customHeight="1">
+      <x:c r="A45" s="6" t="str">
+        <x:v>Limpopo</x:v>
+      </x:c>
+      <x:c r="B45" s="6" t="str">
         <x:v>Northam Victim Empowerment</x:v>
       </x:c>
-      <x:c r="C45" s="5" t="str">
-        <x:v>Limpopo</x:v>
-      </x:c>
-      <x:c r="D45" s="5" t="str">
+      <x:c r="C45" s="6" t="str">
+        <x:v>Limpopo</x:v>
+      </x:c>
+      <x:c r="D45" s="6" t="str">
         <x:v>Northam Comprehensive High School</x:v>
       </x:c>
-      <x:c r="E45" s="7" t="n">
+      <x:c r="E45" s="8" t="n">
         <x:v>1.406</x:v>
       </x:c>
-      <x:c r="F45" s="7" t="n">
+      <x:c r="F45" s="8" t="n">
         <x:v>2.193</x:v>
       </x:c>
     </x:row>
-    <x:row r="46" ht="42" customHeight="1">
-      <x:c r="A46" s="5" t="str">
-        <x:v>Limpopo</x:v>
-      </x:c>
-      <x:c r="B46" s="5" t="str">
+    <x:row r="46" ht="15" customHeight="1">
+      <x:c r="A46" s="6" t="str">
+        <x:v>Limpopo</x:v>
+      </x:c>
+      <x:c r="B46" s="6" t="str">
         <x:v>Northam Victim Empowerment</x:v>
       </x:c>
-      <x:c r="C46" s="5" t="str">
-        <x:v>Limpopo</x:v>
-      </x:c>
-      <x:c r="D46" s="5" t="str">
+      <x:c r="C46" s="6" t="str">
+        <x:v>Limpopo</x:v>
+      </x:c>
+      <x:c r="D46" s="6" t="str">
         <x:v>Krause Primary School</x:v>
       </x:c>
-      <x:c r="E46" s="7" t="n">
+      <x:c r="E46" s="8" t="n">
         <x:v>1.302</x:v>
       </x:c>
-      <x:c r="F46" s="7" t="n">
+      <x:c r="F46" s="8" t="n">
         <x:v>2.198</x:v>
       </x:c>
     </x:row>
-    <x:row r="47" ht="42" customHeight="1">
-      <x:c r="A47" s="5" t="str">
-        <x:v>Limpopo</x:v>
-      </x:c>
-      <x:c r="B47" s="5" t="str">
+    <x:row r="47" ht="15" customHeight="1">
+      <x:c r="A47" s="6" t="str">
+        <x:v>Limpopo</x:v>
+      </x:c>
+      <x:c r="B47" s="6" t="str">
         <x:v>Opret Advice Office</x:v>
       </x:c>
-      <x:c r="C47" s="5" t="str">
-        <x:v>Limpopo</x:v>
-      </x:c>
-      <x:c r="D47" s="5" t="str">
+      <x:c r="C47" s="6" t="str">
+        <x:v>Limpopo</x:v>
+      </x:c>
+      <x:c r="D47" s="6" t="str">
         <x:v>Ntata Secondary School</x:v>
       </x:c>
-      <x:c r="E47" s="7" t="n">
+      <x:c r="E47" s="8" t="n">
         <x:v>185.762</x:v>
       </x:c>
-      <x:c r="F47" s="7" t="n">
+      <x:c r="F47" s="8" t="n">
         <x:v>262.499</x:v>
       </x:c>
     </x:row>
-    <x:row r="48" ht="42" customHeight="1">
-      <x:c r="A48" s="5" t="str">
-        <x:v>Limpopo</x:v>
-      </x:c>
-      <x:c r="B48" s="5" t="str">
+    <x:row r="48" ht="15" customHeight="1">
+      <x:c r="A48" s="6" t="str">
+        <x:v>Limpopo</x:v>
+      </x:c>
+      <x:c r="B48" s="6" t="str">
         <x:v>Opret Advice Office</x:v>
       </x:c>
-      <x:c r="C48" s="5" t="str">
-        <x:v>Limpopo</x:v>
-      </x:c>
-      <x:c r="D48" s="5" t="str">
+      <x:c r="C48" s="6" t="str">
+        <x:v>Limpopo</x:v>
+      </x:c>
+      <x:c r="D48" s="6" t="str">
         <x:v>Ithuteng Primary School</x:v>
       </x:c>
-      <x:c r="E48" s="7" t="n">
+      <x:c r="E48" s="8" t="n">
         <x:v>5.316</x:v>
       </x:c>
-      <x:c r="F48" s="7" t="n">
+      <x:c r="F48" s="8" t="n">
         <x:v>6.724</x:v>
       </x:c>
     </x:row>
-    <x:row r="49" ht="42" customHeight="1">
-      <x:c r="A49" s="5" t="str">
-        <x:v>Limpopo</x:v>
-      </x:c>
-      <x:c r="B49" s="5" t="str">
+    <x:row r="49" ht="15" customHeight="1">
+      <x:c r="A49" s="6" t="str">
+        <x:v>Limpopo</x:v>
+      </x:c>
+      <x:c r="B49" s="6" t="str">
         <x:v>Opret Advice Office</x:v>
       </x:c>
-      <x:c r="C49" s="5" t="str">
-        <x:v>Limpopo</x:v>
-      </x:c>
-      <x:c r="D49" s="5" t="str">
+      <x:c r="C49" s="6" t="str">
+        <x:v>Limpopo</x:v>
+      </x:c>
+      <x:c r="D49" s="6" t="str">
         <x:v>Gwenane Secondary School</x:v>
       </x:c>
-      <x:c r="E49" s="7" t="n">
+      <x:c r="E49" s="8" t="n">
         <x:v>1.901</x:v>
       </x:c>
-      <x:c r="F49" s="7" t="n">
+      <x:c r="F49" s="8" t="n">
         <x:v>2.666</x:v>
       </x:c>
     </x:row>
-    <x:row r="50" ht="42" customHeight="1">
-      <x:c r="A50" s="5" t="str">
-        <x:v>Limpopo</x:v>
-      </x:c>
-      <x:c r="B50" s="5" t="str">
+    <x:row r="50" ht="15" customHeight="1">
+      <x:c r="A50" s="6" t="str">
+        <x:v>Limpopo</x:v>
+      </x:c>
+      <x:c r="B50" s="6" t="str">
         <x:v>Mamadi Advice Centre</x:v>
       </x:c>
-      <x:c r="C50" s="5" t="str">
-        <x:v>Limpopo</x:v>
-      </x:c>
-      <x:c r="D50" s="5" t="str">
+      <x:c r="C50" s="6" t="str">
+        <x:v>Limpopo</x:v>
+      </x:c>
+      <x:c r="D50" s="6" t="str">
         <x:v>Thokampe High School</x:v>
       </x:c>
-      <x:c r="E50" s="7" t="n">
+      <x:c r="E50" s="8" t="n">
         <x:v>1.038</x:v>
       </x:c>
-      <x:c r="F50" s="7" t="n">
+      <x:c r="F50" s="8" t="n">
         <x:v>1.486</x:v>
       </x:c>
     </x:row>
-    <x:row r="51" ht="42" customHeight="1">
-      <x:c r="A51" s="5" t="str">
-        <x:v>Limpopo</x:v>
-      </x:c>
-      <x:c r="B51" s="5" t="str">
+    <x:row r="51" ht="15" customHeight="1">
+      <x:c r="A51" s="6" t="str">
+        <x:v>Limpopo</x:v>
+      </x:c>
+      <x:c r="B51" s="6" t="str">
         <x:v>Mamadi Advice Centre</x:v>
       </x:c>
-      <x:c r="C51" s="5" t="str">
-        <x:v>Limpopo</x:v>
-      </x:c>
-      <x:c r="D51" s="5" t="str">
+      <x:c r="C51" s="6" t="str">
+        <x:v>Limpopo</x:v>
+      </x:c>
+      <x:c r="D51" s="6" t="str">
         <x:v>Masete Primary School</x:v>
       </x:c>
-      <x:c r="E51" s="7" t="n">
+      <x:c r="E51" s="8" t="n">
         <x:v>0.604</x:v>
       </x:c>
-      <x:c r="F51" s="7" t="n">
+      <x:c r="F51" s="8" t="n">
         <x:v>1.002</x:v>
       </x:c>
     </x:row>
-    <x:row r="52" ht="42" customHeight="1">
-      <x:c r="A52" s="5" t="str">
-        <x:v>Limpopo</x:v>
-      </x:c>
-      <x:c r="B52" s="5" t="str">
+    <x:row r="52" ht="15" customHeight="1">
+      <x:c r="A52" s="6" t="str">
+        <x:v>Limpopo</x:v>
+      </x:c>
+      <x:c r="B52" s="6" t="str">
         <x:v>Mamadi Advice Centre</x:v>
       </x:c>
-      <x:c r="C52" s="5" t="str">
-        <x:v>Limpopo</x:v>
-      </x:c>
-      <x:c r="D52" s="5" t="str">
+      <x:c r="C52" s="6" t="str">
+        <x:v>Limpopo</x:v>
+      </x:c>
+      <x:c r="D52" s="6" t="str">
         <x:v>Mantshabe Primary School</x:v>
       </x:c>
-      <x:c r="E52" s="7" t="n">
+      <x:c r="E52" s="8" t="n">
         <x:v>2.759</x:v>
       </x:c>
-      <x:c r="F52" s="7" t="n">
+      <x:c r="F52" s="8" t="n">
         <x:v>5.521</x:v>
       </x:c>
     </x:row>
-    <x:row r="53" ht="42" customHeight="1">
-      <x:c r="A53" s="5" t="str">
-        <x:v>Mpumalanga</x:v>
-      </x:c>
-      <x:c r="B53" s="5" t="str">
+    <x:row r="53" ht="15" customHeight="1">
+      <x:c r="A53" s="6" t="str">
+        <x:v>Mpumalanga</x:v>
+      </x:c>
+      <x:c r="B53" s="6" t="str">
         <x:v>Resoketswe Lebjane Foundation</x:v>
       </x:c>
-      <x:c r="C53" s="5" t="str">
-        <x:v>Mpumalanga</x:v>
-      </x:c>
-      <x:c r="D53" s="5" t="str">
+      <x:c r="C53" s="6" t="str">
+        <x:v>Mpumalanga</x:v>
+      </x:c>
+      <x:c r="D53" s="6" t="str">
         <x:v>Hlamalani Primary School</x:v>
       </x:c>
-      <x:c r="E53" s="7" t="n">
+      <x:c r="E53" s="8" t="n">
         <x:v>0.862</x:v>
       </x:c>
-      <x:c r="F53" s="7" t="n">
+      <x:c r="F53" s="8" t="n">
         <x:v>1.097</x:v>
       </x:c>
     </x:row>
-    <x:row r="54" ht="42" customHeight="1">
-      <x:c r="A54" s="5" t="str">
-        <x:v>Mpumalanga</x:v>
-      </x:c>
-      <x:c r="B54" s="5" t="str">
+    <x:row r="54" ht="15" customHeight="1">
+      <x:c r="A54" s="6" t="str">
+        <x:v>Mpumalanga</x:v>
+      </x:c>
+      <x:c r="B54" s="6" t="str">
         <x:v>Resoketswe Lebjane Foundation</x:v>
       </x:c>
-      <x:c r="C54" s="5" t="str">
-        <x:v>Mpumalanga</x:v>
-      </x:c>
-      <x:c r="D54" s="5" t="str">
+      <x:c r="C54" s="6" t="str">
+        <x:v>Mpumalanga</x:v>
+      </x:c>
+      <x:c r="D54" s="6" t="str">
         <x:v>Esselman Primary School</x:v>
       </x:c>
-      <x:c r="E54" s="7" t="n">
+      <x:c r="E54" s="8" t="n">
         <x:v>0.849</x:v>
       </x:c>
-      <x:c r="F54" s="7" t="n">
+      <x:c r="F54" s="8" t="n">
         <x:v>1.035</x:v>
       </x:c>
     </x:row>
-    <x:row r="55" ht="42" customHeight="1">
-      <x:c r="A55" s="5" t="str">
-        <x:v>Mpumalanga</x:v>
-      </x:c>
-      <x:c r="B55" s="5" t="str">
+    <x:row r="55" ht="15" customHeight="1">
+      <x:c r="A55" s="6" t="str">
+        <x:v>Mpumalanga</x:v>
+      </x:c>
+      <x:c r="B55" s="6" t="str">
         <x:v>Resoketswe Lebjane Foundation</x:v>
       </x:c>
-      <x:c r="C55" s="5" t="str">
-        <x:v>Mpumalanga</x:v>
-      </x:c>
-      <x:c r="D55" s="5" t="str">
+      <x:c r="C55" s="6" t="str">
+        <x:v>Mpumalanga</x:v>
+      </x:c>
+      <x:c r="D55" s="6" t="str">
         <x:v>Mkhweyantaba High School</x:v>
       </x:c>
-      <x:c r="E55" s="7" t="n">
+      <x:c r="E55" s="8" t="n">
         <x:v>1.374</x:v>
       </x:c>
-      <x:c r="F55" s="7" t="n">
+      <x:c r="F55" s="8" t="n">
         <x:v>1.371</x:v>
       </x:c>
     </x:row>
-    <x:row r="56" ht="42" customHeight="1">
-      <x:c r="A56" s="5" t="str">
-        <x:v>Mpumalanga</x:v>
-      </x:c>
-      <x:c r="B56" s="5" t="str">
+    <x:row r="56" ht="15" customHeight="1">
+      <x:c r="A56" s="6" t="str">
+        <x:v>Mpumalanga</x:v>
+      </x:c>
+      <x:c r="B56" s="6" t="str">
         <x:v>Grip Trust</x:v>
       </x:c>
-      <x:c r="C56" s="5" t="str">
-        <x:v>Mpumalanga</x:v>
-      </x:c>
-      <x:c r="D56" s="5" t="str">
+      <x:c r="C56" s="6" t="str">
+        <x:v>Mpumalanga</x:v>
+      </x:c>
+      <x:c r="D56" s="6" t="str">
         <x:v>Sibongile Combined School</x:v>
       </x:c>
-      <x:c r="E56" s="7" t="n">
+      <x:c r="E56" s="8" t="n">
         <x:v>34.569</x:v>
       </x:c>
-      <x:c r="F56" s="7" t="n">
+      <x:c r="F56" s="8" t="n">
         <x:v>38.935</x:v>
       </x:c>
     </x:row>
-    <x:row r="57" ht="42" customHeight="1">
-      <x:c r="A57" s="5" t="str">
-        <x:v>Mpumalanga</x:v>
-      </x:c>
-      <x:c r="B57" s="5" t="str">
+    <x:row r="57" ht="15" customHeight="1">
+      <x:c r="A57" s="6" t="str">
+        <x:v>Mpumalanga</x:v>
+      </x:c>
+      <x:c r="B57" s="6" t="str">
         <x:v>Grip Trust</x:v>
       </x:c>
-      <x:c r="C57" s="5" t="str">
-        <x:v>Mpumalanga</x:v>
-      </x:c>
-      <x:c r="D57" s="5" t="str">
+      <x:c r="C57" s="6" t="str">
+        <x:v>Mpumalanga</x:v>
+      </x:c>
+      <x:c r="D57" s="6" t="str">
         <x:v>Masitakhe High School</x:v>
       </x:c>
-      <x:c r="E57" s="7" t="n">
+      <x:c r="E57" s="8" t="n">
         <x:v>38.164</x:v>
       </x:c>
-      <x:c r="F57" s="7" t="n">
+      <x:c r="F57" s="8" t="n">
         <x:v>44.804</x:v>
       </x:c>
     </x:row>
-    <x:row r="58" ht="42" customHeight="1">
-      <x:c r="A58" s="5" t="str">
-        <x:v>Mpumalanga</x:v>
-      </x:c>
-      <x:c r="B58" s="5" t="str">
+    <x:row r="58" ht="15" customHeight="1">
+      <x:c r="A58" s="6" t="str">
+        <x:v>Mpumalanga</x:v>
+      </x:c>
+      <x:c r="B58" s="6" t="str">
         <x:v>Grip Trust</x:v>
       </x:c>
-      <x:c r="C58" s="5" t="str">
-        <x:v>Mpumalanga</x:v>
-      </x:c>
-      <x:c r="D58" s="5" t="str">
+      <x:c r="C58" s="6" t="str">
+        <x:v>Mpumalanga</x:v>
+      </x:c>
+      <x:c r="D58" s="6" t="str">
         <x:v>Vulindlela High School</x:v>
       </x:c>
-      <x:c r="E58" s="7" t="n">
+      <x:c r="E58" s="8" t="n">
         <x:v>20.793</x:v>
       </x:c>
-      <x:c r="F58" s="7" t="n">
+      <x:c r="F58" s="8" t="n">
         <x:v>29.32</x:v>
       </x:c>
     </x:row>
-    <x:row r="59" ht="42" customHeight="1">
-      <x:c r="A59" s="5" t="str">
-        <x:v>Mpumalanga</x:v>
-      </x:c>
-      <x:c r="B59" s="5" t="str">
+    <x:row r="59" ht="15" customHeight="1">
+      <x:c r="A59" s="6" t="str">
+        <x:v>Mpumalanga</x:v>
+      </x:c>
+      <x:c r="B59" s="6" t="str">
         <x:v>Badplaas Shelter</x:v>
       </x:c>
-      <x:c r="C59" s="5" t="str">
-        <x:v>Mpumalanga</x:v>
-      </x:c>
-      <x:c r="D59" s="5" t="str">
+      <x:c r="C59" s="6" t="str">
+        <x:v>Mpumalanga</x:v>
+      </x:c>
+      <x:c r="D59" s="6" t="str">
         <x:v>Sunduza Primary School</x:v>
       </x:c>
-      <x:c r="E59" s="7" t="n">
+      <x:c r="E59" s="8" t="n">
         <x:v>1.89</x:v>
       </x:c>
-      <x:c r="F59" s="7" t="n">
+      <x:c r="F59" s="8" t="n">
         <x:v>2.49</x:v>
       </x:c>
     </x:row>
-    <x:row r="60" ht="42" customHeight="1">
-      <x:c r="A60" s="5" t="str">
-        <x:v>Mpumalanga</x:v>
-      </x:c>
-      <x:c r="B60" s="5" t="str">
+    <x:row r="60" ht="15" customHeight="1">
+      <x:c r="A60" s="6" t="str">
+        <x:v>Mpumalanga</x:v>
+      </x:c>
+      <x:c r="B60" s="6" t="str">
         <x:v>Badplaas Shelter</x:v>
       </x:c>
-      <x:c r="C60" s="5" t="str">
-        <x:v>Mpumalanga</x:v>
-      </x:c>
-      <x:c r="D60" s="5" t="str">
+      <x:c r="C60" s="6" t="str">
+        <x:v>Mpumalanga</x:v>
+      </x:c>
+      <x:c r="D60" s="6" t="str">
         <x:v>Izithandani Primary School</x:v>
       </x:c>
-      <x:c r="E60" s="7" t="n">
+      <x:c r="E60" s="8" t="n">
         <x:v>0.803</x:v>
       </x:c>
-      <x:c r="F60" s="7" t="n">
+      <x:c r="F60" s="8" t="n">
         <x:v>1.432</x:v>
       </x:c>
     </x:row>
-    <x:row r="61" ht="42" customHeight="1">
-      <x:c r="A61" s="5" t="str">
-        <x:v>Mpumalanga</x:v>
-      </x:c>
-      <x:c r="B61" s="5" t="str">
+    <x:row r="61" ht="15" customHeight="1">
+      <x:c r="A61" s="6" t="str">
+        <x:v>Mpumalanga</x:v>
+      </x:c>
+      <x:c r="B61" s="6" t="str">
         <x:v>Badplaas Shelter</x:v>
       </x:c>
-      <x:c r="C61" s="5" t="str">
-        <x:v>Mpumalanga</x:v>
-      </x:c>
-      <x:c r="D61" s="5" t="str">
+      <x:c r="C61" s="6" t="str">
+        <x:v>Mpumalanga</x:v>
+      </x:c>
+      <x:c r="D61" s="6" t="str">
         <x:v>Engabezweni Secondary School</x:v>
       </x:c>
-      <x:c r="E61" s="7" t="n">
+      <x:c r="E61" s="8" t="n">
         <x:v>1.016</x:v>
       </x:c>
-      <x:c r="F61" s="7" t="n">
+      <x:c r="F61" s="8" t="n">
         <x:v>1.265</x:v>
       </x:c>
     </x:row>
-    <x:row r="62" ht="42" customHeight="1">
-      <x:c r="A62" s="5" t="str">
-        <x:v>Mpumalanga</x:v>
-      </x:c>
-      <x:c r="B62" s="5" t="str">
+    <x:row r="62" ht="15" customHeight="1">
+      <x:c r="A62" s="6" t="str">
+        <x:v>Mpumalanga</x:v>
+      </x:c>
+      <x:c r="B62" s="6" t="str">
         <x:v>Isiphephelo Multipurpose Centre</x:v>
       </x:c>
-      <x:c r="C62" s="5" t="str">
-        <x:v>Mpumalanga</x:v>
-      </x:c>
-      <x:c r="D62" s="5" t="str">
+      <x:c r="C62" s="6" t="str">
+        <x:v>Mpumalanga</x:v>
+      </x:c>
+      <x:c r="D62" s="6" t="str">
         <x:v>Kusasalethu Secondary School</x:v>
       </x:c>
-      <x:c r="E62" s="7" t="n">
+      <x:c r="E62" s="8" t="n">
         <x:v>1.245</x:v>
       </x:c>
-      <x:c r="F62" s="7" t="n">
+      <x:c r="F62" s="8" t="n">
         <x:v>1.74</x:v>
       </x:c>
     </x:row>
-    <x:row r="63" ht="42" customHeight="1">
-      <x:c r="A63" s="5" t="str">
-        <x:v>Mpumalanga</x:v>
-      </x:c>
-      <x:c r="B63" s="5" t="str">
+    <x:row r="63" ht="15" customHeight="1">
+      <x:c r="A63" s="6" t="str">
+        <x:v>Mpumalanga</x:v>
+      </x:c>
+      <x:c r="B63" s="6" t="str">
         <x:v>Isiphephelo Multipurpose Centre</x:v>
       </x:c>
-      <x:c r="C63" s="5" t="str">
-        <x:v>Mpumalanga</x:v>
-      </x:c>
-      <x:c r="D63" s="5" t="str">
+      <x:c r="C63" s="6" t="str">
+        <x:v>Mpumalanga</x:v>
+      </x:c>
+      <x:c r="D63" s="6" t="str">
         <x:v>Isibanisesizwe Combined School</x:v>
       </x:c>
-      <x:c r="E63" s="7" t="n">
+      <x:c r="E63" s="8" t="n">
         <x:v>0.016</x:v>
       </x:c>
-      <x:c r="F63" s="7" t="n">
+      <x:c r="F63" s="8" t="n">
         <x:v>0.014</x:v>
       </x:c>
     </x:row>
-    <x:row r="64" ht="42" customHeight="1">
-      <x:c r="A64" s="5" t="str">
-        <x:v>Mpumalanga</x:v>
-      </x:c>
-      <x:c r="B64" s="5" t="str">
+    <x:row r="64" ht="15" customHeight="1">
+      <x:c r="A64" s="6" t="str">
+        <x:v>Mpumalanga</x:v>
+      </x:c>
+      <x:c r="B64" s="6" t="str">
         <x:v>Isiphephelo Multipurpose Centre</x:v>
       </x:c>
-      <x:c r="C64" s="5" t="str">
-        <x:v>Mpumalanga</x:v>
-      </x:c>
-      <x:c r="D64" s="5" t="str">
+      <x:c r="C64" s="6" t="str">
+        <x:v>Mpumalanga</x:v>
+      </x:c>
+      <x:c r="D64" s="6" t="str">
         <x:v>Vukizithathe Primary School</x:v>
       </x:c>
-      <x:c r="E64" s="7" t="n">
+      <x:c r="E64" s="8" t="n">
         <x:v>1.892</x:v>
       </x:c>
-      <x:c r="F64" s="7" t="n">
+      <x:c r="F64" s="8" t="n">
         <x:v>3.34</x:v>
       </x:c>
     </x:row>
-    <x:row r="65" ht="42" customHeight="1">
-      <x:c r="A65" s="5" t="str">
-        <x:v>Mpumalanga</x:v>
-      </x:c>
-      <x:c r="B65" s="5" t="str">
+    <x:row r="65" ht="15" customHeight="1">
+      <x:c r="A65" s="6" t="str">
+        <x:v>Mpumalanga</x:v>
+      </x:c>
+      <x:c r="B65" s="6" t="str">
         <x:v>Emthunzini Victim Empowerment Centre</x:v>
       </x:c>
-      <x:c r="C65" s="5" t="str">
-        <x:v>Mpumalanga</x:v>
-      </x:c>
-      <x:c r="D65" s="5" t="str">
+      <x:c r="C65" s="6" t="str">
+        <x:v>Mpumalanga</x:v>
+      </x:c>
+      <x:c r="D65" s="6" t="str">
         <x:v>Njabulo Combined School</x:v>
       </x:c>
-      <x:c r="E65" s="7" t="n">
+      <x:c r="E65" s="8" t="n">
         <x:v>196.888</x:v>
       </x:c>
-      <x:c r="F65" s="7" t="n">
+      <x:c r="F65" s="8" t="n">
         <x:v>254.306</x:v>
       </x:c>
     </x:row>
-    <x:row r="66" ht="42" customHeight="1">
-      <x:c r="A66" s="5" t="str">
-        <x:v>Mpumalanga</x:v>
-      </x:c>
-      <x:c r="B66" s="5" t="str">
+    <x:row r="66" ht="15" customHeight="1">
+      <x:c r="A66" s="6" t="str">
+        <x:v>Mpumalanga</x:v>
+      </x:c>
+      <x:c r="B66" s="6" t="str">
         <x:v>Emthunzini Victim Empowerment Centre</x:v>
       </x:c>
-      <x:c r="C66" s="5" t="str">
-        <x:v>Mpumalanga</x:v>
-      </x:c>
-      <x:c r="D66" s="5" t="str">
+      <x:c r="C66" s="6" t="str">
+        <x:v>Mpumalanga</x:v>
+      </x:c>
+      <x:c r="D66" s="6" t="str">
         <x:v>Nkukhunda Primary School</x:v>
       </x:c>
-      <x:c r="E66" s="7" t="n">
+      <x:c r="E66" s="8" t="n">
         <x:v>3.024</x:v>
       </x:c>
-      <x:c r="F66" s="7" t="n">
+      <x:c r="F66" s="8" t="n">
         <x:v>4.298</x:v>
       </x:c>
     </x:row>
-    <x:row r="67" ht="42" customHeight="1">
-      <x:c r="A67" s="5" t="str">
+    <x:row r="67" ht="15" customHeight="1">
+      <x:c r="A67" s="6" t="str">
         <x:v>North West</x:v>
       </x:c>
-      <x:c r="B67" s="5" t="str">
+      <x:c r="B67" s="6" t="str">
         <x:v>Letlhabile Network Against Domestic Violence, Child Abuse &amp; HIV AIDS</x:v>
       </x:c>
-      <x:c r="C67" s="5" t="str">
+      <x:c r="C67" s="6" t="str">
         <x:v>North West</x:v>
       </x:c>
-      <x:c r="D67" s="5" t="str">
+      <x:c r="D67" s="6" t="str">
         <x:v>Relebogile Primary School</x:v>
       </x:c>
-      <x:c r="E67" s="7" t="n">
+      <x:c r="E67" s="8" t="n">
         <x:v>26.323</x:v>
       </x:c>
-      <x:c r="F67" s="7" t="n">
+      <x:c r="F67" s="8" t="n">
         <x:v>43.985</x:v>
       </x:c>
     </x:row>
-    <x:row r="68" ht="42" customHeight="1">
-      <x:c r="A68" s="5" t="str">
+    <x:row r="68" ht="15" customHeight="1">
+      <x:c r="A68" s="6" t="str">
         <x:v>North West</x:v>
       </x:c>
-      <x:c r="B68" s="5" t="str">
+      <x:c r="B68" s="6" t="str">
         <x:v>Letlhabile Network Against Domestic Violence, Child Abuse &amp; HIV AIDS</x:v>
       </x:c>
-      <x:c r="C68" s="5" t="str">
+      <x:c r="C68" s="6" t="str">
         <x:v>North West</x:v>
       </x:c>
-      <x:c r="D68" s="5" t="str">
+      <x:c r="D68" s="6" t="str">
         <x:v>Molelwaneng Primary School</x:v>
       </x:c>
-      <x:c r="E68" s="7" t="n">
+      <x:c r="E68" s="8" t="n">
         <x:v>2.41</x:v>
       </x:c>
-      <x:c r="F68" s="7" t="n">
+      <x:c r="F68" s="8" t="n">
         <x:v>3.956</x:v>
       </x:c>
     </x:row>
-    <x:row r="69" ht="42" customHeight="1">
-      <x:c r="A69" s="5" t="str">
+    <x:row r="69" ht="15" customHeight="1">
+      <x:c r="A69" s="6" t="str">
         <x:v>North West</x:v>
       </x:c>
-      <x:c r="B69" s="5" t="str">
+      <x:c r="B69" s="6" t="str">
         <x:v>Letlhabile Network Against Domestic Violence, Child Abuse &amp; HIV AIDS</x:v>
       </x:c>
-      <x:c r="C69" s="5" t="str">
+      <x:c r="C69" s="6" t="str">
         <x:v>North West</x:v>
       </x:c>
-      <x:c r="D69" s="5" t="str">
+      <x:c r="D69" s="6" t="str">
         <x:v>Eletsa Secondary School</x:v>
       </x:c>
-      <x:c r="E69" s="7" t="n">
+      <x:c r="E69" s="8" t="n">
         <x:v>3.295</x:v>
       </x:c>
-      <x:c r="F69" s="7" t="n">
+      <x:c r="F69" s="8" t="n">
         <x:v>5.141</x:v>
       </x:c>
     </x:row>
-    <x:row r="70" ht="42" customHeight="1">
-      <x:c r="A70" s="5" t="str">
+    <x:row r="70" ht="15" customHeight="1">
+      <x:c r="A70" s="6" t="str">
         <x:v>Northern Cape</x:v>
       </x:c>
-      <x:c r="B70" s="5" t="str">
+      <x:c r="B70" s="6" t="str">
         <x:v>Ethembeni (Place of Hope) Community Centre</x:v>
       </x:c>
-      <x:c r="C70" s="5" t="str">
+      <x:c r="C70" s="6" t="str">
         <x:v>Northern Cape</x:v>
       </x:c>
-      <x:c r="D70" s="5" t="str">
+      <x:c r="D70" s="6" t="str">
         <x:v>Veritas Secondary School</x:v>
       </x:c>
-      <x:c r="E70" s="7" t="n">
+      <x:c r="E70" s="8" t="n">
         <x:v>620.661</x:v>
       </x:c>
-      <x:c r="F70" s="7" t="n">
+      <x:c r="F70" s="8" t="n">
         <x:v>756.047</x:v>
       </x:c>
     </x:row>
-    <x:row r="71" ht="42" customHeight="1">
-      <x:c r="A71" s="5" t="str">
+    <x:row r="71" ht="15" customHeight="1">
+      <x:c r="A71" s="6" t="str">
         <x:v>Northern Cape</x:v>
       </x:c>
-      <x:c r="B71" s="5" t="str">
+      <x:c r="B71" s="6" t="str">
         <x:v>Ethembeni (Place of Hope) Community Centre</x:v>
       </x:c>
-      <x:c r="C71" s="5" t="str">
+      <x:c r="C71" s="6" t="str">
         <x:v>Northern Cape</x:v>
       </x:c>
-      <x:c r="D71" s="5" t="str">
+      <x:c r="D71" s="6" t="str">
         <x:v>Kareeville Primere Skool</x:v>
       </x:c>
-      <x:c r="E71" s="7" t="n">
+      <x:c r="E71" s="8" t="n">
         <x:v>2.001</x:v>
       </x:c>
-      <x:c r="F71" s="7" t="n">
+      <x:c r="F71" s="8" t="n">
         <x:v>3.003</x:v>
       </x:c>
     </x:row>
-    <x:row r="72" ht="42" customHeight="1">
-      <x:c r="A72" s="5" t="str">
+    <x:row r="72" ht="15" customHeight="1">
+      <x:c r="A72" s="6" t="str">
         <x:v>Northern Cape</x:v>
       </x:c>
-      <x:c r="B72" s="5" t="str">
+      <x:c r="B72" s="6" t="str">
         <x:v>Ethembeni (Place of Hope) Community Centre</x:v>
       </x:c>
-      <x:c r="C72" s="5" t="str">
+      <x:c r="C72" s="6" t="str">
         <x:v>Northern Cape</x:v>
       </x:c>
-      <x:c r="D72" s="5" t="str">
+      <x:c r="D72" s="6" t="str">
         <x:v>Alpha Primary School</x:v>
       </x:c>
-      <x:c r="E72" s="7" t="n">
+      <x:c r="E72" s="8" t="n">
         <x:v>609.669</x:v>
       </x:c>
-      <x:c r="F72" s="7" t="n">
+      <x:c r="F72" s="8" t="n">
         <x:v>742.889</x:v>
       </x:c>
     </x:row>
-    <x:row r="73" ht="42" customHeight="1">
-      <x:c r="A73" s="5" t="str">
+    <x:row r="73" ht="15" customHeight="1">
+      <x:c r="A73" s="6" t="str">
         <x:v>Western Cape</x:v>
       </x:c>
-      <x:c r="B73" s="5" t="str">
+      <x:c r="B73" s="6" t="str">
         <x:v>Callas Foundation</x:v>
       </x:c>
-      <x:c r="C73" s="5" t="str">
+      <x:c r="C73" s="6" t="str">
         <x:v>Western Cape</x:v>
       </x:c>
-      <x:c r="D73" s="5" t="str">
+      <x:c r="D73" s="6" t="str">
         <x:v>Bridgeville Primary School</x:v>
       </x:c>
-      <x:c r="E73" s="7" t="n">
+      <x:c r="E73" s="8" t="n">
         <x:v>0.189</x:v>
       </x:c>
-      <x:c r="F73" s="7" t="n">
+      <x:c r="F73" s="8" t="n">
         <x:v>0.188</x:v>
       </x:c>
     </x:row>
-    <x:row r="74" ht="42" customHeight="1">
-      <x:c r="A74" s="5" t="str">
+    <x:row r="74" ht="15" customHeight="1">
+      <x:c r="A74" s="6" t="str">
         <x:v>Western Cape</x:v>
       </x:c>
-      <x:c r="B74" s="5" t="str">
+      <x:c r="B74" s="6" t="str">
         <x:v>Callas Foundation</x:v>
       </x:c>
-      <x:c r="C74" s="5" t="str">
+      <x:c r="C74" s="6" t="str">
         <x:v>Western Cape</x:v>
       </x:c>
-      <x:c r="D74" s="5" t="str">
+      <x:c r="D74" s="6" t="str">
         <x:v>Cypress Primary School</x:v>
       </x:c>
-      <x:c r="E74" s="7" t="n">
+      <x:c r="E74" s="8" t="n">
         <x:v>1.106</x:v>
       </x:c>
-      <x:c r="F74" s="7" t="n">
+      <x:c r="F74" s="8" t="n">
         <x:v>1.316</x:v>
       </x:c>
     </x:row>
-    <x:row r="75" ht="42" customHeight="1">
-      <x:c r="A75" s="5" t="str">
+    <x:row r="75" ht="15" customHeight="1">
+      <x:c r="A75" s="6" t="str">
         <x:v>Western Cape</x:v>
       </x:c>
-      <x:c r="B75" s="5" t="str">
+      <x:c r="B75" s="6" t="str">
         <x:v>Callas Foundation</x:v>
       </x:c>
-      <x:c r="C75" s="5" t="str">
+      <x:c r="C75" s="6" t="str">
         <x:v>Western Cape</x:v>
       </x:c>
-      <x:c r="D75" s="5" t="str">
+      <x:c r="D75" s="6" t="str">
         <x:v>Bokmakierie Primary School</x:v>
       </x:c>
-      <x:c r="E75" s="7" t="n">
+      <x:c r="E75" s="8" t="n">
         <x:v>2.539</x:v>
       </x:c>
-      <x:c r="F75" s="7" t="n">
+      <x:c r="F75" s="8" t="n">
         <x:v>4.183</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb4b6818d64d340c6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R04e5215cf7ed46cc"/>
   </x:tableParts>
 </x:worksheet>
 </file>